--- a/UHR.SW.xlsx
+++ b/UHR.SW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00EB218-9F44-4BD9-8656-F8583C69FA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F21153B-376F-4508-A8E4-0156783F2BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{B503D4ED-6C28-4F3F-8B49-F2AD3EFBCEC1}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{B503D4ED-6C28-4F3F-8B49-F2AD3EFBCEC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -715,7 +715,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>140.1</v>
+        <v>194.55</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -741,7 +741,7 @@
       </c>
       <c r="I5" s="5">
         <f>+I3*I4</f>
-        <v>7229.7596279999998</v>
+        <v>10039.612674000002</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -774,7 +774,7 @@
       </c>
       <c r="I8" s="5">
         <f>+I5-I6+I7</f>
-        <v>6140.7596279999998</v>
+        <v>8950.6126740000018</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">

--- a/UHR.SW.xlsx
+++ b/UHR.SW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F21153B-376F-4508-A8E4-0156783F2BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6755D9B4-2020-434F-A283-B6B93A0708CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{B503D4ED-6C28-4F3F-8B49-F2AD3EFBCEC1}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{B503D4ED-6C28-4F3F-8B49-F2AD3EFBCEC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>Swatch Group</t>
   </si>
@@ -201,9 +201,6 @@
     <t>Interest Expense</t>
   </si>
   <si>
-    <t>non-operating result</t>
-  </si>
-  <si>
     <t>Pretax Income</t>
   </si>
   <si>
@@ -229,9 +226,6 @@
   </si>
   <si>
     <t>Founded: 1983</t>
-  </si>
-  <si>
-    <t>Q225</t>
   </si>
   <si>
     <t>H122</t>
@@ -263,22 +257,44 @@
   <si>
     <t>Corporate</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>Non-operating result</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Revenue Growth</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -323,6 +339,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -341,27 +364,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -715,33 +747,34 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>194.55</v>
+        <v>177.95</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>51.604280000000003</v>
+        <f>28.861731+(115.212126*0.2)</f>
+        <v>51.904156200000003</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>64</v>
+      <c r="J4" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I5" s="5">
         <f>+I3*I4</f>
-        <v>10039.612674000002</v>
+        <v>9236.3445957900003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -749,11 +782,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="5">
-        <f>1031+245</f>
-        <v>1276</v>
+        <f>1010+221</f>
+        <v>1231</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>64</v>
+      <c r="J6" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -761,11 +794,11 @@
         <v>6</v>
       </c>
       <c r="I7" s="5">
-        <f>185+2</f>
-        <v>187</v>
+        <f>36+2</f>
+        <v>38</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>64</v>
+      <c r="J7" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -774,17 +807,17 @@
       </c>
       <c r="I8" s="5">
         <f>+I5-I6+I7</f>
-        <v>8950.6126740000018</v>
+        <v>8043.3445957900003</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -907,28 +940,28 @@
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>29</v>
@@ -947,6 +980,9 @@
       </c>
       <c r="Q2" s="6" t="s">
         <v>34</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.2">
@@ -972,7 +1008,9 @@
       <c r="Q3" s="5">
         <v>1868</v>
       </c>
-      <c r="R3" s="5"/>
+      <c r="R3" s="5">
+        <v>1847</v>
+      </c>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
@@ -1050,7 +1088,9 @@
       <c r="Q4" s="5">
         <v>3555</v>
       </c>
-      <c r="R4" s="5"/>
+      <c r="R4" s="5">
+        <v>3002</v>
+      </c>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -1128,7 +1168,9 @@
       <c r="Q5" s="5">
         <v>1118</v>
       </c>
-      <c r="R5" s="5"/>
+      <c r="R5" s="5">
+        <v>1307</v>
+      </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1206,7 +1248,9 @@
       <c r="Q6" s="5">
         <v>93</v>
       </c>
-      <c r="R6" s="5"/>
+      <c r="R6" s="5">
+        <v>94</v>
+      </c>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1284,7 +1328,9 @@
       <c r="Q7" s="5">
         <v>31</v>
       </c>
-      <c r="R7" s="5"/>
+      <c r="R7" s="5">
+        <v>30</v>
+      </c>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1350,11 +1396,17 @@
       <c r="G8" s="5">
         <v>3300</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5">
+        <f>+Q8-G8</f>
+        <v>3118</v>
+      </c>
       <c r="I8" s="5">
         <v>2887</v>
       </c>
-      <c r="J8" s="5"/>
+      <c r="J8" s="5">
+        <f>+R8-I8</f>
+        <v>3047</v>
+      </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -1366,7 +1418,9 @@
       <c r="Q8" s="5">
         <v>6418</v>
       </c>
-      <c r="R8" s="5"/>
+      <c r="R8" s="5">
+        <v>5934</v>
+      </c>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -1432,11 +1486,17 @@
       <c r="G9" s="5">
         <v>153</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5">
+        <f>+Q9-G9</f>
+        <v>177</v>
+      </c>
       <c r="I9" s="5">
         <v>178</v>
       </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="5">
+        <f>+R9-I9</f>
+        <v>181</v>
+      </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1448,7 +1508,9 @@
       <c r="Q9" s="5">
         <v>330</v>
       </c>
-      <c r="R9" s="5"/>
+      <c r="R9" s="5">
+        <v>359</v>
+      </c>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
@@ -1505,7 +1567,7 @@
     </row>
     <row r="10" spans="1:71" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1514,11 +1576,17 @@
       <c r="G10" s="5">
         <v>4</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5">
+        <f>+Q10-G10</f>
+        <v>4</v>
+      </c>
       <c r="I10" s="5">
         <v>4</v>
       </c>
-      <c r="J10" s="5"/>
+      <c r="J10" s="5">
+        <f>+R10-I10</f>
+        <v>4</v>
+      </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -1530,7 +1598,9 @@
       <c r="Q10" s="5">
         <v>8</v>
       </c>
-      <c r="R10" s="5"/>
+      <c r="R10" s="5">
+        <v>8</v>
+      </c>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -1596,11 +1666,17 @@
       <c r="G11" s="5">
         <v>-12</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="5">
+        <f>+Q11-G11</f>
+        <v>-9</v>
+      </c>
       <c r="I11" s="5">
         <v>-10</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="5">
+        <f>+R11-I11</f>
+        <v>-11</v>
+      </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -1612,7 +1688,9 @@
       <c r="Q11" s="5">
         <v>-21</v>
       </c>
-      <c r="R11" s="5"/>
+      <c r="R11" s="5">
+        <v>-21</v>
+      </c>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
@@ -1678,11 +1756,16 @@
       <c r="G12" s="9">
         <v>3445</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="H12" s="9">
+        <v>3445</v>
+      </c>
       <c r="I12" s="9">
         <v>3059</v>
       </c>
-      <c r="J12" s="9"/>
+      <c r="J12" s="9">
+        <f>+R12-I12</f>
+        <v>3221</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1694,7 +1777,9 @@
       <c r="Q12" s="9">
         <v>6735</v>
       </c>
-      <c r="R12" s="5"/>
+      <c r="R12" s="9">
+        <v>6280</v>
+      </c>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
@@ -1760,11 +1845,17 @@
       <c r="G13" s="5">
         <v>61</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5">
+        <f>+Q13-G13</f>
+        <v>202</v>
+      </c>
       <c r="I13" s="5">
         <v>68</v>
       </c>
-      <c r="J13" s="5"/>
+      <c r="J13" s="5">
+        <f>+R13-I13</f>
+        <v>47</v>
+      </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -1776,7 +1867,9 @@
       <c r="Q13" s="5">
         <v>263</v>
       </c>
-      <c r="R13" s="5"/>
+      <c r="R13" s="5">
+        <v>115</v>
+      </c>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -1842,11 +1935,17 @@
       <c r="G14" s="5">
         <v>268</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5">
+        <f>+Q14-G14</f>
+        <v>-55</v>
+      </c>
       <c r="I14" s="5">
         <v>43</v>
       </c>
-      <c r="J14" s="5"/>
+      <c r="J14" s="5">
+        <f>+R14-I14</f>
+        <v>-88</v>
+      </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -1858,7 +1957,9 @@
       <c r="Q14" s="5">
         <v>213</v>
       </c>
-      <c r="R14" s="5"/>
+      <c r="R14" s="5">
+        <v>-45</v>
+      </c>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -1924,11 +2025,17 @@
       <c r="G15" s="5">
         <v>798</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5">
+        <f>+Q15-G15</f>
+        <v>547</v>
+      </c>
       <c r="I15" s="5">
         <v>549</v>
       </c>
-      <c r="J15" s="5"/>
+      <c r="J15" s="5">
+        <f>+R15-I15</f>
+        <v>524</v>
+      </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
@@ -1940,7 +2047,9 @@
       <c r="Q15" s="5">
         <v>1345</v>
       </c>
-      <c r="R15" s="5"/>
+      <c r="R15" s="5">
+        <v>1073</v>
+      </c>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2006,11 +2115,17 @@
       <c r="G16" s="5">
         <v>1316</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5">
+        <f>+Q16-G16</f>
+        <v>1190</v>
+      </c>
       <c r="I16" s="5">
         <v>1227</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5">
+        <f>+R16-I16</f>
+        <v>1155</v>
+      </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -2022,7 +2137,9 @@
       <c r="Q16" s="5">
         <v>2506</v>
       </c>
-      <c r="R16" s="5"/>
+      <c r="R16" s="5">
+        <v>2382</v>
+      </c>
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2103,7 +2220,7 @@
       </c>
       <c r="H17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1855</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -2111,7 +2228,7 @@
       </c>
       <c r="J17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1501</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5">
@@ -2138,7 +2255,10 @@
         <f>+Q12+SUM(Q13:Q14)-SUM(Q15:Q16)</f>
         <v>3360</v>
       </c>
-      <c r="R17" s="5"/>
+      <c r="R17" s="5">
+        <f>+R12+SUM(R13:R14)-SUM(R15:R16)</f>
+        <v>2895</v>
+      </c>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
@@ -2204,11 +2324,17 @@
       <c r="G18" s="5">
         <v>177</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5">
+        <f>+Q18-G18</f>
+        <v>191</v>
+      </c>
       <c r="I18" s="5">
         <v>186</v>
       </c>
-      <c r="J18" s="5"/>
+      <c r="J18" s="5">
+        <f>+R18-I18</f>
+        <v>191</v>
+      </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -2220,7 +2346,9 @@
       <c r="Q18" s="5">
         <v>368</v>
       </c>
-      <c r="R18" s="5"/>
+      <c r="R18" s="5">
+        <v>377</v>
+      </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2286,11 +2414,17 @@
       <c r="G19" s="5">
         <v>25</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5">
+        <f>+Q19-G19</f>
+        <v>23</v>
+      </c>
       <c r="I19" s="5">
         <v>22</v>
       </c>
-      <c r="J19" s="5"/>
+      <c r="J19" s="5">
+        <f>+R19-I19</f>
+        <v>24</v>
+      </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
@@ -2302,7 +2436,9 @@
       <c r="Q19" s="5">
         <v>48</v>
       </c>
-      <c r="R19" s="5"/>
+      <c r="R19" s="5">
+        <v>46</v>
+      </c>
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2368,11 +2504,17 @@
       <c r="G20" s="5">
         <v>1254</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5">
+        <f>+Q20-G20</f>
+        <v>1386</v>
+      </c>
       <c r="I20" s="5">
         <v>1118</v>
       </c>
-      <c r="J20" s="5"/>
+      <c r="J20" s="5">
+        <f>+R20-I20</f>
+        <v>1219</v>
+      </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -2384,7 +2526,9 @@
       <c r="Q20" s="5">
         <v>2640</v>
       </c>
-      <c r="R20" s="5"/>
+      <c r="R20" s="5">
+        <v>2337</v>
+      </c>
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2459,7 +2603,7 @@
       </c>
       <c r="H21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
@@ -2467,7 +2611,7 @@
       </c>
       <c r="J21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5">
@@ -2494,7 +2638,10 @@
         <f>+Q17-SUM(Q18:Q20)</f>
         <v>304</v>
       </c>
-      <c r="R21" s="5"/>
+      <c r="R21" s="5">
+        <f>+R17-SUM(R18:R20)</f>
+        <v>135</v>
+      </c>
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -2560,11 +2707,17 @@
       <c r="G22" s="5">
         <v>22</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5">
+        <f>+Q22-G22</f>
+        <v>22</v>
+      </c>
       <c r="I22" s="5">
         <v>-8</v>
       </c>
-      <c r="J22" s="5"/>
+      <c r="J22" s="5">
+        <f>+R22-I22</f>
+        <v>17</v>
+      </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -2576,7 +2729,9 @@
       <c r="Q22" s="5">
         <v>44</v>
       </c>
-      <c r="R22" s="5"/>
+      <c r="R22" s="5">
+        <v>9</v>
+      </c>
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -2642,11 +2797,17 @@
       <c r="G23" s="5">
         <v>1</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5">
+        <f>+Q23-G23</f>
+        <v>2</v>
+      </c>
       <c r="I23" s="5">
         <v>1</v>
       </c>
-      <c r="J23" s="5"/>
+      <c r="J23" s="5">
+        <f>+R23-I23</f>
+        <v>3</v>
+      </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
@@ -2658,7 +2819,9 @@
       <c r="Q23" s="5">
         <v>3</v>
       </c>
-      <c r="R23" s="5"/>
+      <c r="R23" s="5">
+        <v>4</v>
+      </c>
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -2715,7 +2878,7 @@
     </row>
     <row r="24" spans="2:71" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2724,11 +2887,17 @@
       <c r="G24" s="5">
         <v>1</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="5">
+        <f>+Q24-G24</f>
+        <v>1</v>
+      </c>
       <c r="I24" s="5">
         <v>-4</v>
       </c>
-      <c r="J24" s="5"/>
+      <c r="J24" s="5">
+        <f>+R24-I24</f>
+        <v>-4</v>
+      </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
@@ -2740,7 +2909,9 @@
       <c r="Q24" s="5">
         <v>2</v>
       </c>
-      <c r="R24" s="5"/>
+      <c r="R24" s="5">
+        <v>-8</v>
+      </c>
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -2796,8 +2967,8 @@
       <c r="BS24" s="5"/>
     </row>
     <row r="25" spans="2:71" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>54</v>
+      <c r="B25" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2806,11 +2977,17 @@
       <c r="G25" s="5">
         <v>1</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="5">
+        <f>+Q25-G25</f>
+        <v>1</v>
+      </c>
       <c r="I25" s="5">
         <v>9</v>
       </c>
-      <c r="J25" s="5"/>
+      <c r="J25" s="5">
+        <f>+R25-I25</f>
+        <v>1</v>
+      </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -2822,7 +2999,9 @@
       <c r="Q25" s="5">
         <v>2</v>
       </c>
-      <c r="R25" s="5"/>
+      <c r="R25" s="5">
+        <v>10</v>
+      </c>
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -2879,7 +3058,7 @@
     </row>
     <row r="26" spans="2:71" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="5">
         <f t="shared" ref="C26:J26" si="4">+C21+C22-C23-C24+C25</f>
@@ -2903,7 +3082,7 @@
       </c>
       <c r="H26" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="I26" s="5">
         <f>+I21+I22-I23-I24+I25</f>
@@ -2911,7 +3090,7 @@
       </c>
       <c r="J26" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5">
@@ -2938,7 +3117,10 @@
         <f>+Q21+Q22-Q23-Q24+Q25</f>
         <v>345</v>
       </c>
-      <c r="R26" s="5"/>
+      <c r="R26" s="5">
+        <f>+R21+R22-R23-R24+R25</f>
+        <v>158</v>
+      </c>
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -2995,7 +3177,7 @@
     </row>
     <row r="27" spans="2:71" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3004,11 +3186,17 @@
       <c r="G27" s="5">
         <v>78</v>
       </c>
-      <c r="H27" s="5"/>
+      <c r="H27" s="5">
+        <f>+Q27-G27</f>
+        <v>48</v>
+      </c>
       <c r="I27" s="5">
         <v>55</v>
       </c>
-      <c r="J27" s="5"/>
+      <c r="J27" s="5">
+        <f>+R27-I27</f>
+        <v>78</v>
+      </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -3020,7 +3208,9 @@
       <c r="Q27" s="5">
         <v>126</v>
       </c>
-      <c r="R27" s="5"/>
+      <c r="R27" s="5">
+        <v>133</v>
+      </c>
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3077,7 +3267,7 @@
     </row>
     <row r="28" spans="2:71" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="5">
         <f t="shared" ref="C28:J28" si="6">+C26-C27</f>
@@ -3101,7 +3291,7 @@
       </c>
       <c r="H28" s="5">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="6"/>
@@ -3109,7 +3299,7 @@
       </c>
       <c r="J28" s="5">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5">
@@ -3136,7 +3326,10 @@
         <f>+Q26-Q27</f>
         <v>219</v>
       </c>
-      <c r="R28" s="5"/>
+      <c r="R28" s="5">
+        <f>+R26-R27</f>
+        <v>25</v>
+      </c>
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3193,7 +3386,7 @@
     </row>
     <row r="29" spans="2:71" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3202,11 +3395,17 @@
       <c r="G29" s="5">
         <v>11</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="5">
+        <f>+Q29-G29</f>
+        <v>15</v>
+      </c>
       <c r="I29" s="5">
         <v>3</v>
       </c>
-      <c r="J29" s="5"/>
+      <c r="J29" s="5">
+        <f>+R29-I29</f>
+        <v>0</v>
+      </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -3218,7 +3417,9 @@
       <c r="Q29" s="5">
         <v>26</v>
       </c>
-      <c r="R29" s="5"/>
+      <c r="R29" s="5">
+        <v>3</v>
+      </c>
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3275,7 +3476,7 @@
     </row>
     <row r="30" spans="2:71" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
@@ -3296,7 +3497,7 @@
       </c>
       <c r="H30" s="5">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="8"/>
@@ -3304,7 +3505,7 @@
       </c>
       <c r="J30" s="5">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5">
@@ -3331,7 +3532,10 @@
         <f>+Q28-Q29</f>
         <v>193</v>
       </c>
-      <c r="R30" s="5"/>
+      <c r="R30" s="5">
+        <f>+R28-R29</f>
+        <v>22</v>
+      </c>
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3458,6 +3662,9 @@
       <c r="BS31" s="5"/>
     </row>
     <row r="32" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B32" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -3472,8 +3679,14 @@
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
+      <c r="Q32" s="12">
+        <f>+Q30/Q33</f>
+        <v>1.6778622824374443</v>
+      </c>
+      <c r="R32" s="12">
+        <f>+R30/R33</f>
+        <v>0.19095212252224214</v>
+      </c>
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -3528,7 +3741,10 @@
       <c r="BR32" s="5"/>
       <c r="BS32" s="5"/>
     </row>
-    <row r="33" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B33" s="10" t="s">
+        <v>3</v>
+      </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -3543,8 +3759,12 @@
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
+      <c r="Q33" s="5">
+        <v>115.02731900000001</v>
+      </c>
+      <c r="R33" s="5">
+        <v>115.212126</v>
+      </c>
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -3599,7 +3819,7 @@
       <c r="BR33" s="5"/>
       <c r="BS33" s="5"/>
     </row>
-    <row r="34" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -3670,23 +3890,44 @@
       <c r="BR34" s="5"/>
       <c r="BS34" s="5"/>
     </row>
-    <row r="35" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:71" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
+      <c r="G35" s="14" t="e">
+        <f t="shared" ref="G35:I35" si="10">+G12/E12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H35" s="14" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I35" s="14">
+        <f t="shared" si="10"/>
+        <v>-0.11204644412191578</v>
+      </c>
+      <c r="J35" s="14">
+        <f>+J12/H12-1</f>
+        <v>-6.5021770682148095E-2</v>
+      </c>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
+      <c r="Q35" s="14">
+        <f>+Q12/P12-1</f>
+        <v>-0.14617139959432046</v>
+      </c>
+      <c r="R35" s="14">
+        <f>+R12/Q12-1</f>
+        <v>-6.7557535263548574E-2</v>
+      </c>
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
@@ -3741,23 +3982,56 @@
       <c r="BR35" s="5"/>
       <c r="BS35" s="5"/>
     </row>
-    <row r="36" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
+      <c r="G36" s="13">
+        <f t="shared" ref="G36:J36" si="11">+G17/G12</f>
+        <v>0.48185776487663279</v>
+      </c>
+      <c r="H36" s="13">
+        <f t="shared" si="11"/>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="I36" s="13">
+        <f t="shared" si="11"/>
+        <v>0.4557044785877738</v>
+      </c>
+      <c r="J36" s="13">
+        <f>+J17/J12</f>
+        <v>0.46600434647624961</v>
+      </c>
       <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
+      <c r="L36" s="13" t="e">
+        <f t="shared" ref="L36:R36" si="12">+L17/L12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M36" s="13" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N36" s="13" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O36" s="13" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P36" s="13">
+        <f t="shared" si="12"/>
+        <v>0.54475152129817439</v>
+      </c>
+      <c r="Q36" s="13">
+        <f t="shared" si="12"/>
+        <v>0.49888641425389757</v>
+      </c>
+      <c r="R36" s="13">
+        <f t="shared" si="12"/>
+        <v>0.4609872611464968</v>
+      </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -3812,23 +4086,56 @@
       <c r="BR36" s="5"/>
       <c r="BS36" s="5"/>
     </row>
-    <row r="37" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
+      <c r="G37" s="13">
+        <f t="shared" ref="G37:J37" si="13">+G21/G12</f>
+        <v>5.9216255442670535E-2</v>
+      </c>
+      <c r="H37" s="13">
+        <f t="shared" si="13"/>
+        <v>7.4020319303338175E-2</v>
+      </c>
+      <c r="I37" s="13">
+        <f t="shared" si="13"/>
+        <v>2.2229486760379207E-2</v>
+      </c>
+      <c r="J37" s="13">
+        <f>+J21/J12</f>
+        <v>2.0800993480285624E-2</v>
+      </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
+      <c r="L37" s="13" t="e">
+        <f t="shared" ref="L37:R37" si="14">+L21/L12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M37" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N37" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O37" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P37" s="13">
+        <f t="shared" si="14"/>
+        <v>0.15098884381338742</v>
+      </c>
+      <c r="Q37" s="13">
+        <f t="shared" si="14"/>
+        <v>4.5137342242019304E-2</v>
+      </c>
+      <c r="R37" s="13">
+        <f t="shared" si="14"/>
+        <v>2.1496815286624203E-2</v>
+      </c>
       <c r="S37" s="5"/>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -3883,23 +4190,56 @@
       <c r="BR37" s="5"/>
       <c r="BS37" s="5"/>
     </row>
-    <row r="38" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
+      <c r="G38" s="13">
+        <f t="shared" ref="G38:J38" si="15">+G27/G26</f>
+        <v>0.34666666666666668</v>
+      </c>
+      <c r="H38" s="13">
+        <f t="shared" si="15"/>
+        <v>0.17454545454545456</v>
+      </c>
+      <c r="I38" s="13">
+        <f t="shared" si="15"/>
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="J38" s="13">
+        <f>+J27/J26</f>
+        <v>0.90697674418604646</v>
+      </c>
       <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
+      <c r="L38" s="13" t="e">
+        <f t="shared" ref="L38:R38" si="16">+L27/L26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M38" s="13" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N38" s="13" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O38" s="13" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P38" s="13">
+        <f t="shared" si="16"/>
+        <v>0.22743055555555555</v>
+      </c>
+      <c r="Q38" s="13">
+        <f t="shared" si="16"/>
+        <v>0.36521739130434783</v>
+      </c>
+      <c r="R38" s="13">
+        <f t="shared" si="16"/>
+        <v>0.84177215189873422</v>
+      </c>
       <c r="S38" s="5"/>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -3954,7 +4294,7 @@
       <c r="BR38" s="5"/>
       <c r="BS38" s="5"/>
     </row>
-    <row r="39" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -4025,7 +4365,7 @@
       <c r="BR39" s="5"/>
       <c r="BS39" s="5"/>
     </row>
-    <row r="40" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -4096,7 +4436,7 @@
       <c r="BR40" s="5"/>
       <c r="BS40" s="5"/>
     </row>
-    <row r="41" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -4167,7 +4507,7 @@
       <c r="BR41" s="5"/>
       <c r="BS41" s="5"/>
     </row>
-    <row r="42" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -4238,7 +4578,7 @@
       <c r="BR42" s="5"/>
       <c r="BS42" s="5"/>
     </row>
-    <row r="43" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -4309,7 +4649,7 @@
       <c r="BR43" s="5"/>
       <c r="BS43" s="5"/>
     </row>
-    <row r="44" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -4380,7 +4720,7 @@
       <c r="BR44" s="5"/>
       <c r="BS44" s="5"/>
     </row>
-    <row r="45" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -4451,7 +4791,7 @@
       <c r="BR45" s="5"/>
       <c r="BS45" s="5"/>
     </row>
-    <row r="46" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -4522,7 +4862,7 @@
       <c r="BR46" s="5"/>
       <c r="BS46" s="5"/>
     </row>
-    <row r="47" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -4593,7 +4933,7 @@
       <c r="BR47" s="5"/>
       <c r="BS47" s="5"/>
     </row>
-    <row r="48" spans="3:71" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:71" x14ac:dyDescent="0.2">
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
